--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Id</t>
   </si>
@@ -37,39 +37,6 @@
   <si>
     <t>PriseSetId</t>
   </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>Help</t>
-  </si>
-  <si>
-    <t>「過去改編」解放</t>
-  </si>
-  <si>
-    <t>過去のマスを選び直すことができる</t>
-  </si>
-  <si>
-    <t>「並行世界化」解放・可能回数+1</t>
-  </si>
-  <si>
-    <t>過去のマスを2つ選んだことにできる</t>
-  </si>
-  <si>
-    <t>「初期加入変更」解放</t>
-  </si>
-  <si>
-    <t>初期加入の仲間を変更できる</t>
-  </si>
-  <si>
-    <t>「並行世界化」可能回数+1</t>
-  </si>
-  <si>
-    <t>「レベルリンク」解放</t>
-  </si>
-  <si>
-    <t>Lv降順5位が最低Lvになる</t>
-  </si>
 </sst>
 </file>
 
@@ -77,9 +44,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -90,6 +57,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -99,9 +103,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -113,20 +117,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -135,14 +125,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -159,14 +141,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -180,21 +162,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -219,16 +186,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,187 +210,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,6 +401,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -467,17 +458,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -500,26 +485,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1252,79 +1219,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="31.4545454545455" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -57,6 +57,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -65,8 +79,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -81,19 +96,35 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -106,51 +137,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -162,6 +148,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -171,24 +187,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,13 +210,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -228,79 +378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,85 +390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,11 +404,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -428,21 +434,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -454,6 +445,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -493,11 +495,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,8 +974,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
   </cols>
@@ -1051,30 +1051,30 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1086,128 +1086,59 @@
         <v>8020</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>30010</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>30020</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>30030</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>30</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>8030</v>
-      </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>40010</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>31</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>8030</v>
-      </c>
-      <c r="E9">
-        <v>800</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
         <v>40020</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>8030</v>
-      </c>
-      <c r="E10">
-        <v>600</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>40030</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -58,85 +58,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -148,31 +102,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -188,14 +180,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,55 +210,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,37 +372,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,84 +391,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,57 +404,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -463,8 +416,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,9 +439,41 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,8 +481,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -58,6 +58,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -65,7 +88,106 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -78,128 +200,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -210,181 +210,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,11 +404,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -439,50 +480,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,8 +974,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
   </cols>
@@ -1138,6 +1138,144 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>110</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>8010</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>111</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>8010</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>120</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>8020</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>30010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>121</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>8020</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>130</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>8030</v>
+      </c>
+      <c r="E12">
+        <v>1500</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>131</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>8030</v>
+      </c>
+      <c r="E13">
+        <v>1200</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>40020</v>
       </c>
     </row>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -57,6 +57,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -64,83 +110,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,40 +162,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,6 +177,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -210,37 +210,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -252,73 +366,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,61 +384,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,21 +401,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -430,35 +415,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,6 +457,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -509,7 +509,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -518,7 +518,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,127 +527,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1063,7 +1063,7 @@
         <v>8020</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>8020</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>8020</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>8020</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1276,6 +1276,144 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>210</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>8010</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>211</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>8010</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>220</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>8020</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>30010</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>221</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>8020</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>230</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>8030</v>
+      </c>
+      <c r="E18">
+        <v>2000</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>231</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>8030</v>
+      </c>
+      <c r="E19">
+        <v>1500</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>40020</v>
       </c>
     </row>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -57,6 +57,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -65,25 +102,63 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -96,65 +171,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -162,40 +178,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,19 +210,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -234,157 +372,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,6 +401,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -415,6 +424,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -437,23 +461,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -478,15 +487,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1063,7 +1063,7 @@
         <v>8020</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>8020</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1109,7 +1109,7 @@
         <v>8030</v>
       </c>
       <c r="E6">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>8030</v>
       </c>
       <c r="E7">
-        <v>800</v>
+        <v>2500</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>8020</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>8020</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>8030</v>
       </c>
       <c r="E12">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>8030</v>
       </c>
       <c r="E13">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>8020</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>8020</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>8030</v>
       </c>
       <c r="E18">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         <v>8030</v>
       </c>
       <c r="E19">
-        <v>1500</v>
+        <v>5500</v>
       </c>
       <c r="F19">
         <v>0</v>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,15 +43,98 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -65,22 +148,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -88,77 +173,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -170,32 +187,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,19 +210,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -234,85 +378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,73 +390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,8 +407,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -424,6 +459,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,50 +501,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1414,6 +1414,167 @@
         <v>0</v>
       </c>
       <c r="G19">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>240</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>2010</v>
+      </c>
+      <c r="E20">
+        <v>201</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>310</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>8010</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>311</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>8010</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>320</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>8020</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>30010</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>321</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>8020</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>330</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>8030</v>
+      </c>
+      <c r="E25">
+        <v>6500</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>331</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>8030</v>
+      </c>
+      <c r="E26">
+        <v>5500</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>40020</v>
       </c>
     </row>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -65,7 +65,114 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -80,22 +187,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -108,98 +200,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -210,43 +210,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,67 +366,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,61 +384,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,6 +401,62 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -415,10 +471,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -447,60 +501,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1143,30 +1143,30 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>8010</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1178,41 +1178,41 @@
         <v>8010</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>30010</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1224,41 +1224,41 @@
         <v>8020</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>30020</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E12">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40010</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1270,312 +1270,381 @@
         <v>8030</v>
       </c>
       <c r="E13">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40020</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4000</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>8010</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>30010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>30020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E18">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>40010</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E19">
-        <v>5500</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>40020</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>2010</v>
+        <v>8030</v>
       </c>
       <c r="E20">
-        <v>201</v>
+        <v>6500</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1100</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>310</v>
+        <v>231</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>5500</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>311</v>
+        <v>241</v>
       </c>
       <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
         <v>4</v>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
       <c r="D22">
-        <v>8010</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>30010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>30020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E25">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>40010</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26">
+        <v>8020</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>330</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
         <v>8030</v>
       </c>
-      <c r="E26">
+      <c r="E27">
+        <v>6500</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>331</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>8030</v>
+      </c>
+      <c r="E28">
         <v>5500</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>40020</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>341</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -44,9 +44,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -57,22 +57,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -86,6 +80,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -95,14 +104,76 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,72 +188,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -192,14 +200,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -210,187 +210,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,6 +401,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -415,6 +433,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -436,11 +469,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -462,42 +493,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,16 +509,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,127 +527,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7">

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -57,14 +57,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -74,14 +111,76 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -95,107 +194,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,187 +210,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,17 +406,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -437,17 +430,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -470,8 +466,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -490,17 +501,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1143,30 +1143,30 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>8010</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1178,41 +1178,41 @@
         <v>8010</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1224,41 +1224,41 @@
         <v>8020</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>30010</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>30020</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1270,381 +1270,289 @@
         <v>8030</v>
       </c>
       <c r="E13">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40010</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>8030</v>
+        <v>8010</v>
       </c>
       <c r="E14">
-        <v>4000</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>8010</v>
+      </c>
+      <c r="E15">
         <v>4</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>6500</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>30010</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>5500</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>30020</v>
+        <v>40020</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>8030</v>
+        <v>8010</v>
       </c>
       <c r="E20">
-        <v>6500</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>40010</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>231</v>
+        <v>311</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>8030</v>
+        <v>8010</v>
       </c>
       <c r="E21">
-        <v>5500</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>40020</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>8020</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1100</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>6500</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>40010</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>5500</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>30010</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>321</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>8020</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>30020</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>330</v>
-      </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>8030</v>
-      </c>
-      <c r="E27">
-        <v>6500</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>40010</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>331</v>
-      </c>
-      <c r="B28">
-        <v>4</v>
-      </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>8030</v>
-      </c>
-      <c r="E28">
-        <v>5500</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
         <v>40020</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>341</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>1100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -58,7 +58,98 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -66,6 +157,29 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -79,52 +193,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -132,74 +200,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -210,187 +210,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +404,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -433,8 +476,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -443,61 +497,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -664,12 +664,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>14015</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>30010</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>30020</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>14015</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>30010</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>30020</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>30010</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>30020</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>30010</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>30020</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1552,6 +1552,282 @@
         <v>0</v>
       </c>
       <c r="G25">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>410</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>8010</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>14033</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>411</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>8010</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>14035</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>420</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>8020</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>421</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>8020</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>430</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>8030</v>
+      </c>
+      <c r="E30">
+        <v>6500</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>431</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>8030</v>
+      </c>
+      <c r="E31">
+        <v>5500</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>40020</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>510</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>8010</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>14033</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>511</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>8010</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>14035</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>520</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>8020</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>521</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>8020</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>530</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>8030</v>
+      </c>
+      <c r="E36">
+        <v>6500</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>40010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>531</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>8030</v>
+      </c>
+      <c r="E37">
+        <v>5500</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>40020</v>
       </c>
     </row>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -57,8 +57,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -72,9 +133,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -88,114 +194,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,43 +210,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,114 +384,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -373,24 +391,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,6 +419,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -439,36 +469,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,7 +509,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -518,136 +518,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1109,13 +1109,13 @@
         <v>8030</v>
       </c>
       <c r="E6">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1132,13 +1132,13 @@
         <v>8030</v>
       </c>
       <c r="E7">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>40010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>40020</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -54,6 +54,103 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -66,16 +163,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -89,115 +193,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -210,90 +210,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -301,96 +391,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,6 +419,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -430,6 +454,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,59 +501,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -509,7 +509,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -518,136 +518,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/EvaluatePrizes.xlsx
+++ b/Assets/Data/EvaluatePrizes.xlsx
@@ -43,10 +43,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -58,14 +58,106 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -81,105 +173,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,11 +187,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -210,61 +210,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,121 +390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,6 +401,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -419,17 +428,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -437,8 +442,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,22 +472,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,145 +509,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -974,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>14015</v>
+        <v>14012</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1069,35 +1069,35 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>10002</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>8020</v>
+        <v>8030</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1109,64 +1109,64 @@
         <v>8030</v>
       </c>
       <c r="E6">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>8030</v>
+        <v>8040</v>
       </c>
       <c r="E7">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>15052</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>14013</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1178,41 +1178,41 @@
         <v>8010</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>14015</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>10002</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1224,13 +1224,13 @@
         <v>8020</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1281,553 +1281,599 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>14023</v>
+        <v>15053</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>14025</v>
+        <v>15052</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>11002</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>11000</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E18">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>50</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E19">
-        <v>5500</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>6500</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>14023</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>5500</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>14025</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>11002</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>11000</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E24">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E25">
-        <v>5500</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>25</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>6500</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>14033</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>411</v>
+        <v>331</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>5500</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>14035</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>12000</v>
+        <v>14033</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B29">
         <v>5</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>11002</v>
+        <v>14035</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B30">
         <v>5</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E30">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>50</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E31">
-        <v>5500</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>25</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>510</v>
+        <v>430</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>6500</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>14033</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>511</v>
+        <v>431</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>8010</v>
+        <v>8030</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>5500</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>14035</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B34">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>12000</v>
+        <v>14033</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>11002</v>
+        <v>14035</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>8030</v>
+        <v>8020</v>
       </c>
       <c r="E36">
-        <v>6500</v>
+        <v>3</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>50</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37">
+        <v>8020</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>530</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38">
         <v>8030</v>
       </c>
-      <c r="E37">
+      <c r="E38">
+        <v>6500</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>531</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>8030</v>
+      </c>
+      <c r="E39">
         <v>5500</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>25</v>
       </c>
     </row>
